--- a/results/Int Task Remove ACC 0.2/Rando_2_permute.xlsx
+++ b/results/Int Task Remove ACC 0.2/Rando_2_permute.xlsx
@@ -440,437 +440,437 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8140242349104989</v>
+        <v>0.7914734836905449</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8195925749804694</v>
+        <v>0.8017560544818451</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8224414931558031</v>
+        <v>0.7996947284399307</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8212823952990727</v>
+        <v>0.7987741018760686</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.811286414637184</v>
+        <v>0.796975306545294</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8091437111511157</v>
+        <v>0.79797731055331</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8190158565719008</v>
+        <v>0.79797731055331</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8155421011514554</v>
+        <v>0.7991845272465836</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8092675463922194</v>
+        <v>0.7988314199019508</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8091953681374047</v>
+        <v>0.7988314199019508</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8091953681374047</v>
+        <v>0.79356806834007</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.814663932384543</v>
+        <v>0.7854706588317879</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.814663932384543</v>
+        <v>0.7746814249968865</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8079456936471814</v>
+        <v>0.7746814249968865</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7710767580358457</v>
+        <v>0.776208490427182</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7234001902109304</v>
+        <v>0.7694753914608878</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7234001902109304</v>
+        <v>0.7386404164260725</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7198358581569919</v>
+        <v>0.7368416210952979</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6312122833237096</v>
+        <v>0.7368416210952979</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6359838320709215</v>
+        <v>0.7340075631488967</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6356880427521709</v>
+        <v>0.7165814680207874</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6356880427521709</v>
+        <v>0.6558102079865946</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6211830440542101</v>
+        <v>0.6522458759326563</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5906551804173318</v>
+        <v>0.6554571006419618</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6154186904883212</v>
+        <v>0.6465982813083795</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5673076378746194</v>
+        <v>0.6465982813083795</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5619204510716348</v>
+        <v>0.6494563986730524</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5277044201397145</v>
+        <v>0.6295068951462246</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5067861712124815</v>
+        <v>0.6277229600443825</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5071152191388426</v>
+        <v>0.6271554408251532</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.4887833576758036</v>
+        <v>0.6278616555144187</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.502889253082436</v>
+        <v>0.6243270439183451</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5082283210488774</v>
+        <v>0.6216741392389299</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5058287478912628</v>
+        <v>0.5769554646015194</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5043257418792387</v>
+        <v>0.5685622657744868</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4994968751061445</v>
+        <v>0.6079694700134732</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.498790660416879</v>
+        <v>0.6447074940842137</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5104708003577777</v>
+        <v>0.6655556876464794</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.512121701029177</v>
+        <v>0.666171325702252</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5689012205201363</v>
+        <v>0.6488322690578898</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5689012205201363</v>
+        <v>0.6478302650498737</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5780098332257736</v>
+        <v>0.6488322690578898</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.486371047179104</v>
+        <v>0.6354863682166593</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.485870045175096</v>
+        <v>0.5359348640784394</v>
       </c>
     </row>
     <row r="46">
@@ -880,447 +880,447 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4835794470296525</v>
+        <v>0.5245356532273586</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4846055104559401</v>
+        <v>0.5244783352014764</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4853931025893595</v>
+        <v>0.5377244602198747</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4912239733704697</v>
+        <v>0.5407120738652447</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5000941147832388</v>
+        <v>0.5400058591759791</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5075518268174768</v>
+        <v>0.5389465371420807</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5007670708648937</v>
+        <v>0.5435496699613918</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4921962569206209</v>
+        <v>0.5568382527767399</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4808692243243549</v>
+        <v>0.5389203548339617</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4871345798942518</v>
+        <v>0.5053843562831878</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4919393872490744</v>
+        <v>0.5220561178854884</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5005045401537538</v>
+        <v>0.5220561178854884</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5005045401537538</v>
+        <v>0.5250861893278082</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4975317867373165</v>
+        <v>0.5288649332563432</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4972784552155157</v>
+        <v>0.5180962206899675</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4981417637534957</v>
+        <v>0.5175952186859595</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4943481595960282</v>
+        <v>0.5463023504636391</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4939950522513955</v>
+        <v>0.5600494774860455</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4915806188648483</v>
+        <v>0.5329062078960181</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4910222988349581</v>
+        <v>0.5088283912457683</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5191116696670176</v>
+        <v>0.5052364616238125</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5227906377727206</v>
+        <v>0.5217865108748571</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.522356152983934</v>
+        <v>0.4914879193415079</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5204427216013949</v>
+        <v>0.5292371466096034</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5221325419199981</v>
+        <v>0.5084002751265242</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5146083126705389</v>
+        <v>0.5034659714910046</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5185830700949923</v>
+        <v>0.5073593514713042</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5201674535511701</v>
+        <v>0.502120059327695</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5180396102940343</v>
+        <v>0.4969954032358502</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5086684668772573</v>
+        <v>0.4778278308028486</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5001181742015104</v>
+        <v>0.4751749261234333</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4970215855439693</v>
+        <v>0.4721115960735029</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4970215855439693</v>
+        <v>0.4621340137902925</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5002328102532749</v>
+        <v>0.4626923338201827</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5009390249425405</v>
+        <v>0.4813610271390238</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4980717083885285</v>
+        <v>0.4762547694258574</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4966260204023867</v>
+        <v>0.4766319361887617</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4966260204023867</v>
+        <v>0.4778872717185784</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4983582985179398</v>
+        <v>0.4819766651947964</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4976520838286743</v>
+        <v>0.483503730625092</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5044035811736467</v>
+        <v>0.4894159788503561</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5047566885182795</v>
+        <v>0.4850307960553876</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5045182172254112</v>
+        <v>0.502599124803279</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5040172152214032</v>
+        <v>0.502197898622103</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.502185161283018</v>
+        <v>0.5047842860862969</v>
       </c>
     </row>
   </sheetData>
